--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N60_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N60_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>59.68939503644753</v>
+        <v>9.699526693422724</v>
       </c>
       <c r="D2" t="n">
-        <v>59.47885408209776</v>
+        <v>9.665313788340887</v>
       </c>
       <c r="E2" t="n">
-        <v>13.82298143173157</v>
+        <v>2.24623448265638</v>
       </c>
       <c r="F2" t="n">
-        <v>13.757054899611</v>
+        <v>2.235521421186788</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>39.38515631090484</v>
+        <v>6.400087900522037</v>
       </c>
       <c r="D3" t="n">
-        <v>39.97932257464591</v>
+        <v>6.49663991837996</v>
       </c>
       <c r="E3" t="n">
-        <v>13.82298143173157</v>
+        <v>2.24623448265638</v>
       </c>
       <c r="F3" t="n">
-        <v>13.757054899611</v>
+        <v>2.235521421186788</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>31.08644436344698</v>
+        <v>5.051547209060134</v>
       </c>
       <c r="D4" t="n">
-        <v>30.20796709700827</v>
+        <v>4.908794653263843</v>
       </c>
       <c r="E4" t="n">
-        <v>13.82298143173157</v>
+        <v>2.24623448265638</v>
       </c>
       <c r="F4" t="n">
-        <v>13.757054899611</v>
+        <v>2.235521421186788</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>24.96447864873556</v>
+        <v>4.056727780419529</v>
       </c>
       <c r="D5" t="n">
-        <v>25.89372738602619</v>
+        <v>4.207730700229256</v>
       </c>
       <c r="E5" t="n">
-        <v>13.82298143173157</v>
+        <v>2.24623448265638</v>
       </c>
       <c r="F5" t="n">
-        <v>13.757054899611</v>
+        <v>2.235521421186788</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>57.07568609257113</v>
+        <v>9.274798990042807</v>
       </c>
       <c r="D6" t="n">
-        <v>57.4948886490534</v>
+        <v>9.342919405471179</v>
       </c>
       <c r="E6" t="n">
-        <v>13.82298143173157</v>
+        <v>2.24623448265638</v>
       </c>
       <c r="F6" t="n">
-        <v>13.757054899611</v>
+        <v>2.235521421186788</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
